--- a/plantillas/consulta/Listado_Proyectos.xlsx
+++ b/plantillas/consulta/Listado_Proyectos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1CD9B24-CA47-41D4-946A-3FD5E2389B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642FCD46-888A-46C0-BDE8-DA87145BFC7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -198,9 +198,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -209,6 +206,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -541,8 +541,8 @@
       <c r="M1" s="2"/>
     </row>
     <row r="2" spans="1:13" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
@@ -552,9 +552,9 @@
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
     </row>
-    <row r="3" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
+    <row r="3" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
@@ -571,8 +571,8 @@
       <c r="K4" s="4"/>
     </row>
     <row r="5" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
@@ -584,8 +584,8 @@
       <c r="K5" s="5"/>
     </row>
     <row r="6" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -599,8 +599,9 @@
       <c r="F7" s="1"/>
       <c r="G7" s="7"/>
     </row>
-    <row r="8" spans="1:13" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="13"/>
+    <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="G8" s="8" t="s">
